--- a/xls2rdf-lib/src/test/resources/excel/suite/_52_wrapper/input.xlsx
+++ b/xls2rdf-lib/src/test/resources/excel/suite/_52_wrapper/input.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t xml:space="preserve">URI of ConceptScheme</t>
   </si>
@@ -53,6 +53,15 @@
   </si>
   <si>
     <t>hide</t>
+  </si>
+  <si>
+    <t>http://labs.sparna.fr/skos-play/convert/test/concept_2</t>
+  </si>
+  <si>
+    <t>b</t>
+  </si>
+  <si>
+    <t>http://exemple.fr/1</t>
   </si>
 </sst>
 </file>
@@ -117,7 +126,7 @@
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -131,6 +140,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf fontId="3" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -666,9 +678,15 @@
       </c>
     </row>
     <row r="7" ht="12.75" customHeight="1">
-      <c r="A7" s="3"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
+      <c r="A7" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="8" ht="12.75" customHeight="1">
       <c r="A8" s="3"/>
@@ -690,6 +708,8 @@
     <hyperlink r:id="rId3" ref="A5"/>
     <hyperlink r:id="rId4" ref="C5"/>
     <hyperlink r:id="rId5" ref="A6"/>
+    <hyperlink r:id="rId6" ref="A7"/>
+    <hyperlink r:id="rId7" ref="C7"/>
   </hyperlinks>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.78750000000000009" right="0.78750000000000009" top="1.052778" bottom="1.052778" header="0.78750000000000009" footer="0.78750000000000009"/>
